--- a/debug/excel_overviews/gpt-4.1_vs_Llama-2-7b-chat-hf/Llama-3.3-70B-Instruct/default/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Llama-2-7b-chat-hf/Llama-3.3-70B-Instruct/default/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>358</v>
+        <v>318</v>
       </c>
       <c r="D2">
-        <v>7</v>
+        <v>72</v>
       </c>
       <c r="E2">
+        <v>36</v>
+      </c>
+      <c r="G2">
         <v>0</v>
-      </c>
-      <c r="G2">
-        <v>61</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>265</v>
+        <v>405</v>
       </c>
       <c r="D3">
-        <v>113</v>
+        <v>10</v>
       </c>
       <c r="E3">
+        <v>10</v>
+      </c>
+      <c r="G3">
         <v>1</v>
-      </c>
-      <c r="G3">
-        <v>47</v>
       </c>
       <c r="H3">
         <v>426</v>

--- a/debug/excel_overviews/gpt-4.1_vs_Llama-2-7b-chat-hf/Llama-3.3-70B-Instruct/default/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Llama-2-7b-chat-hf/Llama-3.3-70B-Instruct/default/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>318</v>
+        <v>309</v>
       </c>
       <c r="D2">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="E2">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>405</v>
+        <v>412</v>
       </c>
       <c r="D3">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E3">
         <v>10</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H3">
         <v>426</v>
